--- a/lib/sas_test_kit/requirements/Requirements.xlsx
+++ b/lib/sas_test_kit/requirements/Requirements.xlsx
@@ -5,19 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://esantegouv-my.sharepoint.com/personal/arthur_oldrati_esante_gouv_fr/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://esantegouv-my.sharepoint.com/personal/arthur_oldrati_esante_gouv_fr/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0315295-F950-4B1A-BD8C-264E4724F387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{B08BBC4C-7106-4C0F-8C99-265D60E666D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78B9C01F-1B75-4C0F-BF46-FCEA5012DE12}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
     <sheet name="Requirements" sheetId="5" r:id="rId2"/>
-    <sheet name="Metadata" sheetId="3" r:id="rId3"/>
-    <sheet name="Change Log" sheetId="8" r:id="rId4"/>
-    <sheet name="Column Data" sheetId="7" r:id="rId5"/>
+    <sheet name="Cahier de recette" sheetId="10" r:id="rId3"/>
+    <sheet name="Metadata" sheetId="3" r:id="rId4"/>
+    <sheet name="Change Log" sheetId="8" r:id="rId5"/>
+    <sheet name="Column Data" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="235">
   <si>
     <t>ID*</t>
   </si>
@@ -721,106 +722,15 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/sas/StructureDefinition-BundleAgregateur.html</t>
   </si>
   <si>
-    <t xml:space="preserve">Servers SHALL support mutual TLS authentication for all incoming requests.
-</t>
-  </si>
-  <si>
-    <t>Servers SHALL filter Slot resources based on the start date search parameters.</t>
-  </si>
-  <si>
-    <t>Servers SHALL verify certificate OU.</t>
-  </si>
-  <si>
-    <t>Servers SHALL verify certificate CNAME.</t>
-  </si>
-  <si>
-    <t>Servers SHALL support the following interaction : Search</t>
-  </si>
-  <si>
-    <t>Slot resources SHALL NOT have a start date in the past.</t>
-  </si>
-  <si>
-    <t>[When no Slot is available in the requested time window Servers SHALL ] return an empty Bundle</t>
-  </si>
-  <si>
-    <t>Servers SHALL return Slot resources within the requested time window.</t>
-  </si>
-  <si>
-    <t>[When searching for Slot server SHALL] return Slot with Slot.status set to 'free' .</t>
-  </si>
-  <si>
-    <t>Slot resources SHALL have Slot.start and Slot.end.</t>
-  </si>
-  <si>
     <t>When parameter status=free is used in the search interaction</t>
   </si>
   <si>
-    <t>Slot resources MUST include Slot.schedule reference.</t>
-  </si>
-  <si>
-    <t>Slot resources SHALL conform to the FrSlotAgregateur profile.</t>
-  </si>
-  <si>
-    <t>Bundle resource SHALL conform to the BundleAgregateur profile.</t>
-  </si>
-  <si>
-    <t>[When searching for Slot server SHALL] return a Bundle with Bundle.type set to 'searchset'</t>
-  </si>
-  <si>
-    <t>[When searching for Slot server SHALL] include a Practitioner resource in the returned Bundle.</t>
-  </si>
-  <si>
     <t>when a practitioner has at least one free slot during the requested time window</t>
   </si>
   <si>
-    <t>Practitioner.identifier.value MUST be identifier a 12-digit number starting with '8'.</t>
-  </si>
-  <si>
-    <t>Practitioner resources MUST have Practitioner.identifier set with the national identifier (RPPS or ADELI).</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.value MUST be the RPPS identifier of the practitioner</t>
-  </si>
-  <si>
-    <t>PractitionerRole resources MUST have PractitionerRole.organization.identifier set with a FINESS/SIRET identifier.</t>
-  </si>
-  <si>
-    <t>[When searching for Slot server SHALL]  include a PractitionerRole resource.</t>
-  </si>
-  <si>
-    <t>PractitionerRole resources MUST link to a practitioner resources using PractitionerRole.practitioner.reference.</t>
-  </si>
-  <si>
-    <t>PractitionerRole resources MUST contain a Location resources.</t>
-  </si>
-  <si>
-    <t>Slot resources MUST have Slot.serviceType populated with consultation types.</t>
-  </si>
-  <si>
-    <t>Slot resources MUST have Slot.meta.security field set with codes representing slot types.</t>
-  </si>
-  <si>
-    <t>[Slot resources with status set to free MUST] have Slot.comment set to a booking URL.</t>
-  </si>
-  <si>
     <t>when slot resources has status set to free</t>
   </si>
   <si>
-    <t>Servers SHALL support search on Slot resources using start query parameters.</t>
-  </si>
-  <si>
-    <t>Servers SHALL support search on Slot resources using status query parameters.</t>
-  </si>
-  <si>
-    <t>Servers SHALL support search on Slot resources using _include query parameters.</t>
-  </si>
-  <si>
-    <t>Servers SHALL support search on Slot resources using schedule.actor:Practitioner.identifer query parameters.</t>
-  </si>
-  <si>
-    <t>Servers SHALL support search on Slot resources using _include:iterate query parameters.</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/sas/StructureDefinition-FrSlotAgregateur.html</t>
   </si>
   <si>
@@ -833,30 +743,12 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/sas/StructureDefinition-FrPractitionerAgregateur.html</t>
   </si>
   <si>
-    <t>PractitionerRole resources SHALL conform to the FrPractitionerRoleExerciceAgregateur profile</t>
-  </si>
-  <si>
-    <t>Practitioner resources SHALL conform to the FrPractitionerAgregateur profile</t>
-  </si>
-  <si>
-    <t>[When a Practitioner has a name in the server database it SHALL] populate the Practitioner.name element</t>
-  </si>
-  <si>
     <t>When a Practitioner has a name in the server database</t>
   </si>
   <si>
     <t>Is covered by Inferno ?</t>
   </si>
   <si>
-    <t>[When a Practitioner has a phone number in the server database it SHALL] set the Practitioner.telecom.system field to "phone"</t>
-  </si>
-  <si>
-    <t>[When a Practitioner has a phone number in the server database it SHALL] populate the Practitioner.telecom.value (it must respect this format : +N°indicatifXXXXXXXXX)</t>
-  </si>
-  <si>
-    <t>[When a Practitioner does not have  a phone number in the server database it SHALL NOT] have a Practitioner.telecom field</t>
-  </si>
-  <si>
     <t>When a Practitioner has a phone number in the server database</t>
   </si>
   <si>
@@ -864,15 +756,334 @@
   </si>
   <si>
     <t>agg-psindiv</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>MTLS</t>
+  </si>
+  <si>
+    <t>Filtre par date</t>
+  </si>
+  <si>
+    <t>Gestion des informations du PS</t>
+  </si>
+  <si>
+    <t>Gestion des ID nationaux de structure</t>
+  </si>
+  <si>
+    <t>Gestion des adresses</t>
+  </si>
+  <si>
+    <t>Gestion de la prise de RDV</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels</t>
+  </si>
+  <si>
+    <t>Critère d'interfaçage</t>
+  </si>
+  <si>
+    <t>MTLS - 1</t>
+  </si>
+  <si>
+    <t>Filtre par date - 1</t>
+  </si>
+  <si>
+    <t>Gestion des ID nationaux de structure - 1</t>
+  </si>
+  <si>
+    <t>Gestion de la prise de RDV - 1</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 1</t>
+  </si>
+  <si>
+    <t>Filtre par date - 2</t>
+  </si>
+  <si>
+    <t>Filtre par date - 3</t>
+  </si>
+  <si>
+    <t>Filtre par date - 4</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 1</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 2</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 3</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 4</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 5</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 6</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 7</t>
+  </si>
+  <si>
+    <t>Gestion des informations de PS - 8</t>
+  </si>
+  <si>
+    <t>Gestion des ID nationaux de structure - 2</t>
+  </si>
+  <si>
+    <t>Gestion des ID nationaux de structure - 3</t>
+  </si>
+  <si>
+    <t>Gestion des addresses - 1</t>
+  </si>
+  <si>
+    <t>Gestion des addresses - 2</t>
+  </si>
+  <si>
+    <t>Gestion des addresses - 3</t>
+  </si>
+  <si>
+    <t>Gestion des addresses - 4</t>
+  </si>
+  <si>
+    <t>Gestion des addresses - 5</t>
+  </si>
+  <si>
+    <t>Gestion de la prise de RDV - 2</t>
+  </si>
+  <si>
+    <t>Gestion de la prise de RDV - 3</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 2</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 3</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 4</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 5</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 6</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 7</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 8</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 9</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 10</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 11</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 12</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 13</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 14</t>
+  </si>
+  <si>
+    <t>Gestion des champs optionnels - 15</t>
+  </si>
+  <si>
+    <t>Critère d'interfaçage - 1</t>
+  </si>
+  <si>
+    <t>Critère d'interfaçage - 2</t>
+  </si>
+  <si>
+    <t>Critère d'interfaçage - 3</t>
+  </si>
+  <si>
+    <t>ID Test(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les ressources PractitionerRole doivent possèder un champ Practitioner.contained contenant une ressource Location avec un champ adress.line renseigné </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les ressources PractitionerRole doivent possèder un champ Practitioner.contained contenant une ressource Location avec un champ adress.city renseigné </t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent possèder un champ Practitioner.contained contenant une ressource Location avec un champ adress.postalCode correctement renseigné ([0-9]{5})</t>
+  </si>
+  <si>
+    <t>Les motifs associé à chaque créneau sont transmis au niveau de l'élément Slot.speciality</t>
+  </si>
+  <si>
+    <t>[Quand plusieurs PS remontent dans une seul recherche] le Bundle doit être cohérent au niveau de la cardinalité de ses ressources</t>
+  </si>
+  <si>
+    <t>[Quand un PS exerce dans plusieurs lieux] le Bundle doit être cohérent au niveau de la cardinalité de ses ressources</t>
+  </si>
+  <si>
+    <t>[Quand un PS exerce dans plusieurs lieux] le Bundle doit être cohérent au niveau des références entre ses ressources</t>
+  </si>
+  <si>
+    <t>Les champs start et end d'une ressource Slot doivent respecter le format suivant : "AAAA-MM-DDTHH:MM:SS.000+0X:00"</t>
+  </si>
+  <si>
+    <t>Le type des créneaux doit être transmis au niveau de l'élément meta.security.code de la ressource Slot</t>
+  </si>
+  <si>
+    <t>Les indisponibilitées  ne doivent pas être transmises</t>
+  </si>
+  <si>
+    <t>Le type des consultation doit être transmis au niveau de l'élément serviceType.coding.code de la ressource Slot</t>
+  </si>
+  <si>
+    <t>L'information de la nécessité de prendre ou non rendez-vous pour un créneau est transmise au niveau de l'élément appointmentType.coding.code de la ressource Slot</t>
+  </si>
+  <si>
+    <t>Les serveurs doivent supporter la méthode d'authentification mTLS pour tout les requêtes entrantes.</t>
+  </si>
+  <si>
+    <t>[Dans le cadre de la vérification mTLS les serveurs ] doivent vérifier le CNAME du certificat.</t>
+  </si>
+  <si>
+    <t>[Dans le cadre de la vérification mTLS les serveurs] doivent vérifier l'OU du certificat.</t>
+  </si>
+  <si>
+    <t>Le serveur doit être capable de supporter l'interaction 'Search' sur la ressource Slot.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche sur une ressource Slot est effectuée avec le paramètre start=, les ressources Slot retournées ] ne doivent pas avoir d'élément start antérieure à la date du paramètre homonyme.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche sur une ressource Slot est effectuée le serveur ] doit filtrer les ressources Slot retournées.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche sur une ressource Slot est effectuée, la ressource Slot retournée ] doit appartenir à l'intervalle de temps passé en paramètre de la requête.</t>
+  </si>
+  <si>
+    <t>[Lorsque aucun créneau n'est disponible dans la période demandée, le serveur] doit renvoyer un Bundle vide.</t>
+  </si>
+  <si>
+    <t>Les ressources Slot doivent se conformer au profile FrSlotAgregateur.</t>
+  </si>
+  <si>
+    <t>Les ressources Slot doivent possèder un élément start et end.</t>
+  </si>
+  <si>
+    <t>Les ressources Slot doivent possèder un élément schedule.reference.</t>
+  </si>
+  <si>
+    <t>Les ressources Bundle doivent se conformer au profile BundleAgregateur.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche sur une ressource Slot est effectuée avec le paramètre status=free, les ressources Slot retournées ] doivent avoir l'élément status défini sur 'free'.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche sur une ressource Slot est effectuée le serveur] doit renvoyer un Bundle avec l'élélment type défini sur 'searchset'.</t>
+  </si>
+  <si>
+    <t>Lorqu'un practitioner a au moins un créneau de libre sur la période en question</t>
+  </si>
+  <si>
+    <t>Les ressources Practitioner doivent avoir l'élément identifier renseigné avec un identifiant national (RPPS).</t>
+  </si>
+  <si>
+    <t>Les ressources Practitioner doivent avoir l'élément identifier.value défini comme un nombre à 12 chiffres commençant par 8.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche de créneau est effectuée le serveur] doit renvoyer un Bundle possèdant au minimum un Practitioner.</t>
+  </si>
+  <si>
+    <t>[Lorsqu'une recherche de créneau est effectuée le serveur] doit renvoyer un Bundle possèdant au minimum une ressource PractitionerRole.</t>
+  </si>
+  <si>
+    <t>L'élément identifier.value de la ressource Practitioner doit être le RPPS du PS.</t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent possèder un élément organization.identifier défini avec un FINESS/SIRET.</t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent référencer une ressource Practitioner grâce à l'élément practitioner.reference.</t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent possèder un élément contained possèdant une ressource Location.</t>
+  </si>
+  <si>
+    <t>L'élément meta.security des ressources Slots  doit représenter le type de consultation (ex: PUBLIC, PRO, SNP).</t>
+  </si>
+  <si>
+    <t>L'élément serviceType des ressources Slot doit être peuplé avec des type de consultations (ex: AMB, HH, VR).</t>
+  </si>
+  <si>
+    <t>[Les ressources Slot avec l'élément status défini à 'free' doivent] avoir leur élément comment défini comme une URL de prise de rendez-vous.</t>
+  </si>
+  <si>
+    <t>Le serveur doit supporter l'intéraction 'Search' sur les ressources Slot avec le paramètre 'start'.</t>
+  </si>
+  <si>
+    <t>Le serveur doit supporter l'intéraction 'Search' sur les ressources Slot avec le paramètre 'status'.</t>
+  </si>
+  <si>
+    <t>Le serveur doit supporter l'intéraction 'Search' sur les ressources Slot avec le paramètre '_include'.</t>
+  </si>
+  <si>
+    <t>Le serveur doit supporter l'intéraction 'Search' sur les ressources Slot avec le paramètre 'schedule.actor:Practitioner.identifer'.</t>
+  </si>
+  <si>
+    <t>Le serveur doit supporter l'intéraction 'Search' sur les ressources Slot avec le paramètre '_include:iterate'.</t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent se conformer au profil FrPractitionerRoleExerciceAgregateur.</t>
+  </si>
+  <si>
+    <t>Les ressources Practitioner doivent se conformer au profil FrPractitionerAgregateur.</t>
+  </si>
+  <si>
+    <t>[Quand un praticien a un numéro de téléphone dans la solution éditeur] la ressource Practitioner associée doit avoir l'élément telecom.value défini avec le numéro de téléphone présent dans la solution au format suivant : +N°indicatifXXXXXXXXX .</t>
+  </si>
+  <si>
+    <t>[Quand un praticien a un numéro de téléphone dans la solution éditeur] la ressource Practitioner associée doit avoir l'élément telecom.system défini à 'phone'.</t>
+  </si>
+  <si>
+    <t>[Quand un praticien n'a pas de numéro de téléphone enregistré dans la solution éditeur] la ressource Practitioner associée ne doit pas avoir d'élément telecom.</t>
+  </si>
+  <si>
+    <t>[Quand un praticien a un nom dans la solution éditeur] la ressource Practitioner associée doit avoir l'élément name défini avec le nom présent dans la solution.</t>
+  </si>
+  <si>
+    <t>Les ressources PractitionerRole doivent avoir un élément contained contenant une ressource Location défini avec les valeurs existantes dans la solution éditeur.</t>
+  </si>
+  <si>
+    <t>Pourcentage du cahier de recette couvert par Inferno</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -968,8 +1179,20 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1030,8 +1253,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1095,20 +1330,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1116,12 +1360,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1131,77 +1375,95 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1549,117 +1811,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
       <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="37"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="38"/>
+      <c r="C3" s="42"/>
       <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="38"/>
+      <c r="C4" s="42"/>
       <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="39"/>
+      <c r="C5" s="43"/>
       <c r="D5" s="16"/>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="16"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="38"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="16"/>
     </row>
     <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A8" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="38"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="16"/>
     </row>
     <row r="9" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="38"/>
+      <c r="C9" s="42"/>
       <c r="D9" s="16"/>
     </row>
     <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.4">
       <c r="A10" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="38"/>
+      <c r="C10" s="42"/>
       <c r="D10" s="16"/>
     </row>
     <row r="11" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="38"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="16"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1912,58 +2174,53 @@
       <c r="D33" s="16"/>
     </row>
     <row r="34" spans="1:4" ht="21" x14ac:dyDescent="0.5">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
       <c r="D34" s="16"/>
     </row>
     <row r="35" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="40"/>
+      <c r="C35" s="38"/>
     </row>
     <row r="36" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="42"/>
+      <c r="C36" s="40"/>
     </row>
     <row r="37" spans="1:4" ht="112" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="40"/>
+      <c r="C37" s="38"/>
       <c r="D37" s="16"/>
     </row>
     <row r="38" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C38" s="40"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="B2:C2"/>
@@ -1976,6 +2233,11 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2006,7 +2268,7 @@
     <col min="19" max="19" width="9.9140625" style="10" customWidth="1"/>
     <col min="20" max="20" width="6.5" style="10" customWidth="1"/>
     <col min="21" max="21" width="19.83203125" style="6" customWidth="1"/>
-    <col min="22" max="22" width="11" style="6" customWidth="1"/>
+    <col min="22" max="22" width="67.6640625" style="6" customWidth="1"/>
     <col min="23" max="24" width="10.83203125" style="6"/>
     <col min="25" max="25" width="14.83203125" style="6" customWidth="1"/>
     <col min="26" max="16384" width="10.83203125" style="6"/>
@@ -2074,7 +2336,10 @@
         <v>19</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>160</v>
+        <v>127</v>
+      </c>
+      <c r="V1" s="44" t="s">
+        <v>183</v>
       </c>
       <c r="Z1" s="6"/>
     </row>
@@ -2086,7 +2351,7 @@
         <v>115</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>20</v>
@@ -2122,6 +2387,10 @@
       <c r="U2" s="8" t="s">
         <v>22</v>
       </c>
+      <c r="V2" s="44" t="str">
+        <f>'Cahier de recette'!A2</f>
+        <v>MTLS - 1</v>
+      </c>
       <c r="Y2" s="13"/>
       <c r="Z2" s="14"/>
       <c r="AD2" s="14"/>
@@ -2134,7 +2403,7 @@
         <v>115</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>20</v>
@@ -2170,11 +2439,14 @@
       <c r="U3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="V3" s="13"/>
+      <c r="V3" s="13" t="str">
+        <f>'Cahier de recette'!A2</f>
+        <v>MTLS - 1</v>
+      </c>
       <c r="Z3" s="14"/>
       <c r="AD3" s="14"/>
     </row>
-    <row r="4" spans="1:36" ht="16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:36" ht="32" x14ac:dyDescent="0.4">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2182,7 +2454,7 @@
         <v>115</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -2206,6 +2478,10 @@
       </c>
       <c r="U4" s="8" t="s">
         <v>22</v>
+      </c>
+      <c r="V4" s="13" t="str">
+        <f>'Cahier de recette'!A2</f>
+        <v>MTLS - 1</v>
       </c>
       <c r="Z4" s="14"/>
       <c r="AA4" s="5"/>
@@ -2226,7 +2502,7 @@
         <v>116</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2259,13 +2535,13 @@
       <c r="AE5" s="5"/>
       <c r="AF5" s="5"/>
     </row>
-    <row r="6" spans="1:36" ht="32" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" ht="80" x14ac:dyDescent="0.4">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="8" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>50</v>
@@ -2289,6 +2565,10 @@
       </c>
       <c r="U6" s="8" t="s">
         <v>22</v>
+      </c>
+      <c r="V6" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A3:A5)</f>
+        <v>Filtre par date - 1;Filtre par date - 2;Filtre par date - 3</v>
       </c>
       <c r="Z6" s="14"/>
       <c r="AA6" s="5"/>
@@ -2298,7 +2578,7 @@
       <c r="AE6" s="5"/>
       <c r="AF6" s="5"/>
     </row>
-    <row r="7" spans="1:36" ht="32" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:36" ht="48" x14ac:dyDescent="0.4">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2306,7 +2586,7 @@
         <v>116</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2339,7 +2619,7 @@
       <c r="AE7" s="5"/>
       <c r="AF7" s="5"/>
     </row>
-    <row r="8" spans="1:36" ht="32" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" ht="64" x14ac:dyDescent="0.4">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2347,7 +2627,7 @@
         <v>116</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>20</v>
@@ -2381,12 +2661,12 @@
       <c r="AE8" s="5"/>
       <c r="AF8" s="5"/>
     </row>
-    <row r="9" spans="1:36" ht="32" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" ht="48" x14ac:dyDescent="0.4">
       <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -2414,16 +2694,20 @@
       <c r="U9" s="8" t="s">
         <v>22</v>
       </c>
+      <c r="V9" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A6)</f>
+        <v>Filtre par date - 4</v>
+      </c>
     </row>
     <row r="10" spans="1:36" ht="32" x14ac:dyDescent="0.4">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
@@ -2449,7 +2733,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="48" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:36" ht="64" x14ac:dyDescent="0.4">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2457,7 +2741,7 @@
         <v>116</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -2469,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>22</v>
@@ -2485,16 +2769,20 @@
       <c r="U11" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:36" ht="16" x14ac:dyDescent="0.4">
+      <c r="V11" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A23)</f>
+        <v>Gestion de la prise de RDV - 1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" ht="32" x14ac:dyDescent="0.4">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>20</v>
@@ -2525,10 +2813,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>20</v>
@@ -2559,10 +2847,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>20</v>
@@ -2588,7 +2876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="32" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" ht="48" x14ac:dyDescent="0.4">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2596,7 +2884,7 @@
         <v>118</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>20</v>
@@ -2630,7 +2918,7 @@
         <v>116</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>20</v>
@@ -2642,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>22</v>
@@ -2659,15 +2947,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A17" s="7">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>20</v>
@@ -2693,15 +2981,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>136</v>
+        <v>212</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>20</v>
@@ -2726,16 +3014,20 @@
       <c r="U18" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+      <c r="V18" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A7:A8)</f>
+        <v>Gestion des informations de PS - 1;Gestion des informations de PS - 2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="32" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>20</v>
@@ -2760,8 +3052,12 @@
       <c r="U19" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+      <c r="V19" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A7:A8)</f>
+        <v>Gestion des informations de PS - 1;Gestion des informations de PS - 2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2769,7 +3065,7 @@
         <v>116</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
@@ -2781,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>22</v>
@@ -2798,15 +3094,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A21" s="7">
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>139</v>
+        <v>216</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>20</v>
@@ -2831,16 +3127,20 @@
       <c r="U21" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+      <c r="V21" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A15:A16)</f>
+        <v>Gestion des ID nationaux de structure - 1;Gestion des ID nationaux de structure - 2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A22" s="7">
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>20</v>
@@ -2867,15 +3167,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A23" s="7">
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>20</v>
@@ -2900,16 +3200,20 @@
       <c r="U23" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+      <c r="V23" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A18)</f>
+        <v>Gestion des addresses - 1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A24" s="7">
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>20</v>
@@ -2934,16 +3238,20 @@
       <c r="U24" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+      <c r="V24" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A26:A28)</f>
+        <v>Gestion des champs optionnels - 1;Gestion des champs optionnels - 2;Gestion des champs optionnels - 3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A25" s="7">
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>20</v>
@@ -2968,16 +3276,20 @@
       <c r="U25" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+      <c r="V25" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A33:A35)</f>
+        <v>Gestion des champs optionnels - 8;Gestion des champs optionnels - 9;Gestion des champs optionnels - 10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A26" s="7">
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>20</v>
@@ -2989,7 +3301,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>22</v>
@@ -3006,7 +3318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:22" ht="32" x14ac:dyDescent="0.4">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -3014,7 +3326,7 @@
         <v>116</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>20</v>
@@ -3040,7 +3352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:22" ht="32" x14ac:dyDescent="0.4">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -3048,7 +3360,7 @@
         <v>116</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>20</v>
@@ -3074,7 +3386,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:22" ht="32" x14ac:dyDescent="0.4">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -3082,7 +3394,7 @@
         <v>116</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>20</v>
@@ -3108,7 +3420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -3116,7 +3428,7 @@
         <v>116</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>20</v>
@@ -3142,7 +3454,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -3150,7 +3462,7 @@
         <v>116</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>20</v>
@@ -3176,15 +3488,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:22" ht="48" x14ac:dyDescent="0.4">
       <c r="A32" s="7">
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>20</v>
@@ -3210,15 +3522,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="32" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:22" ht="32" x14ac:dyDescent="0.4">
       <c r="A33" s="7">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>20</v>
@@ -3244,12 +3556,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" ht="64" x14ac:dyDescent="0.4">
       <c r="A34" s="7">
         <v>33</v>
       </c>
+      <c r="B34" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="C34" s="8" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>20</v>
@@ -3261,14 +3576,14 @@
         <v>1</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M34" s="9" t="str" cm="1">
         <f t="array" ref="M34">PAGE_NAME(B34)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerAgregateur</v>
       </c>
       <c r="N34" s="9" t="str" cm="1">
         <f t="array" ref="N34">SECTION_NAME(B34)</f>
@@ -3277,13 +3592,20 @@
       <c r="U34" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="64" x14ac:dyDescent="0.4">
+      <c r="V34" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A10)</f>
+        <v>Gestion des informations de PS - 4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="96" x14ac:dyDescent="0.4">
       <c r="A35" s="7">
         <v>34</v>
       </c>
+      <c r="B35" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="C35" s="8" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>20</v>
@@ -3295,14 +3617,14 @@
         <v>1</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M35" s="9" t="str" cm="1">
         <f t="array" ref="M35">PAGE_NAME(B35)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerAgregateur</v>
       </c>
       <c r="N35" s="9" t="str" cm="1">
         <f t="array" ref="N35">SECTION_NAME(B35)</f>
@@ -3311,13 +3633,20 @@
       <c r="U35" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+      <c r="V35" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A11:A12)</f>
+        <v>Gestion des informations de PS - 5;Gestion des informations de PS - 6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="64" x14ac:dyDescent="0.4">
       <c r="A36" s="7">
         <v>35</v>
       </c>
+      <c r="B36" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="C36" s="8" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>20</v>
@@ -3329,14 +3658,14 @@
         <v>1</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M36" s="9" t="str" cm="1">
         <f t="array" ref="M36">PAGE_NAME(B36)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerAgregateur</v>
       </c>
       <c r="N36" s="9" t="str" cm="1">
         <f t="array" ref="N36">SECTION_NAME(B36)</f>
@@ -3345,13 +3674,20 @@
       <c r="U36" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="48" x14ac:dyDescent="0.4">
+      <c r="V36" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A11:A12)</f>
+        <v>Gestion des informations de PS - 5;Gestion des informations de PS - 6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="64" x14ac:dyDescent="0.4">
       <c r="A37" s="7">
         <v>36</v>
       </c>
+      <c r="B37" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="C37" s="8" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>50</v>
@@ -3363,14 +3699,14 @@
         <v>1</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="9" t="str" cm="1">
         <f t="array" ref="M37">PAGE_NAME(B37)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerAgregateur</v>
       </c>
       <c r="N37" s="9" t="str" cm="1">
         <f t="array" ref="N37">SECTION_NAME(B37)</f>
@@ -3379,58 +3715,208 @@
       <c r="U37" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="V37" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A13)</f>
+        <v>Gestion des informations de PS - 7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="74.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="7">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="M38" s="9" t="str" cm="1">
         <f t="array" ref="M38">PAGE_NAME(B38)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerRoleExerciceAgregateur</v>
       </c>
       <c r="N38" s="9" t="str" cm="1">
         <f t="array" ref="N38">SECTION_NAME(B38)</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V38" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A18)</f>
+        <v>Gestion des addresses - 1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="64" x14ac:dyDescent="0.4">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M39" s="9" t="str" cm="1">
         <f t="array" ref="M39">PAGE_NAME(B39)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerRoleExerciceAgregateur</v>
       </c>
       <c r="N39" s="9" t="str" cm="1">
         <f t="array" ref="N39">SECTION_NAME(B39)</f>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U39" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="64" x14ac:dyDescent="0.4">
+      <c r="A40" s="7">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M40" s="9" t="str" cm="1">
         <f t="array" ref="M40">PAGE_NAME(B40)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerRoleExerciceAgregateur</v>
       </c>
       <c r="N40" s="9" t="str" cm="1">
         <f t="array" ref="N40">SECTION_NAME(B40)</f>
         <v/>
       </c>
-    </row>
-    <row r="41" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U40" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="80" x14ac:dyDescent="0.4">
+      <c r="A41" s="7">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M41" s="9" t="str" cm="1">
         <f t="array" ref="M41">PAGE_NAME(B41)</f>
-        <v/>
+        <v>StructureDefinition-FrPractitionerRoleExerciceAgregateur</v>
       </c>
       <c r="N41" s="9" t="str" cm="1">
         <f t="array" ref="N41">SECTION_NAME(B41)</f>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U41" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="32" x14ac:dyDescent="0.4">
+      <c r="A42" s="7">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M42" s="9" t="str" cm="1">
         <f t="array" ref="M42">PAGE_NAME(B42)</f>
-        <v/>
+        <v>StructureDefinition-FrSlotAgregateur</v>
       </c>
       <c r="N42" s="9" t="str" cm="1">
         <f t="array" ref="N42">SECTION_NAME(B42)</f>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U42" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A14)</f>
+        <v>Gestion des informations de PS - 8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A43" s="7">
+        <v>42</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M43" s="9" t="str" cm="1">
         <f t="array" ref="M43">PAGE_NAME(B43)</f>
         <v/>
@@ -3439,8 +3925,33 @@
         <f t="array" ref="N43">SECTION_NAME(B43)</f>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V43" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A21)</f>
+        <v>Gestion des addresses - 4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A44" s="7">
+        <v>43</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M44" s="9" t="str" cm="1">
         <f t="array" ref="M44">PAGE_NAME(B44)</f>
         <v/>
@@ -3449,8 +3960,29 @@
         <f t="array" ref="N44">SECTION_NAME(B44)</f>
         <v/>
       </c>
-    </row>
-    <row r="45" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U44" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A45" s="7">
+        <v>44</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M45" s="9" t="str" cm="1">
         <f t="array" ref="M45">PAGE_NAME(B45)</f>
         <v/>
@@ -3459,29 +3991,110 @@
         <f t="array" ref="N45">SECTION_NAME(B45)</f>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V45" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A22)</f>
+        <v>Gestion des addresses - 5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A46" s="7">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M46" s="9" t="str" cm="1">
         <f t="array" ref="M46">PAGE_NAME(B46)</f>
-        <v/>
+        <v>StructureDefinition-FrSlotAgregateur</v>
       </c>
       <c r="N46" s="9" t="str" cm="1">
         <f t="array" ref="N46">SECTION_NAME(B46)</f>
         <v/>
       </c>
-    </row>
-    <row r="47" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V46" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A24)</f>
+        <v>Gestion de la prise de RDV - 2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A47" s="7">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M47" s="9" t="str" cm="1">
         <f t="array" ref="M47">PAGE_NAME(B47)</f>
-        <v/>
+        <v>StructureDefinition-FrSlotAgregateur</v>
       </c>
       <c r="N47" s="9" t="str" cm="1">
         <f t="array" ref="N47">SECTION_NAME(B47)</f>
         <v/>
       </c>
-    </row>
-    <row r="48" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+      <c r="U47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V47" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A26:A28)</f>
+        <v>Gestion des champs optionnels - 1;Gestion des champs optionnels - 2;Gestion des champs optionnels - 3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="32" x14ac:dyDescent="0.4">
+      <c r="A48" s="7">
+        <v>47</v>
+      </c>
       <c r="B48" s="11"/>
+      <c r="C48" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="M48" s="9" t="str" cm="1">
         <f t="array" ref="M48">PAGE_NAME(B48)</f>
         <v/>
@@ -3490,28 +4103,91 @@
         <f t="array" ref="N48">SECTION_NAME(B48)</f>
         <v/>
       </c>
-    </row>
-    <row r="49" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+      <c r="U48" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="V48" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A29:A31)</f>
+        <v>Gestion des champs optionnels - 4;Gestion des champs optionnels - 5;Gestion des champs optionnels - 6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="48" x14ac:dyDescent="0.4">
+      <c r="A49" s="7">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M49" s="9" t="str" cm="1">
         <f t="array" ref="M49">PAGE_NAME(B49)</f>
-        <v/>
+        <v>StructureDefinition-FrSlotAgregateur</v>
       </c>
       <c r="N49" s="9" t="str" cm="1">
         <f t="array" ref="N49">SECTION_NAME(B49)</f>
         <v/>
       </c>
-    </row>
-    <row r="50" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+      <c r="U49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V49" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A32:A34)</f>
+        <v>Gestion des champs optionnels - 7;Gestion des champs optionnels - 8;Gestion des champs optionnels - 9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="80" x14ac:dyDescent="0.4">
+      <c r="A50" s="7">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="M50" s="9" t="str" cm="1">
         <f t="array" ref="M50">PAGE_NAME(B50)</f>
-        <v/>
+        <v>StructureDefinition-FrSlotAgregateur</v>
       </c>
       <c r="N50" s="9" t="str" cm="1">
         <f t="array" ref="N50">SECTION_NAME(B50)</f>
         <v/>
       </c>
-    </row>
-    <row r="51" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+      <c r="U50" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="V50" s="6" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,'Cahier de recette'!A40)</f>
+        <v>Gestion des champs optionnels - 15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M51" s="9" t="str" cm="1">
         <f t="array" ref="M51">PAGE_NAME(B51)</f>
         <v/>
@@ -3521,7 +4197,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M52" s="9" t="str" cm="1">
         <f t="array" ref="M52">PAGE_NAME(B52)</f>
         <v/>
@@ -3531,7 +4207,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M53" s="9" t="str" cm="1">
         <f t="array" ref="M53">PAGE_NAME(B53)</f>
         <v/>
@@ -3541,7 +4217,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M54" s="9" t="str" cm="1">
         <f t="array" ref="M54">PAGE_NAME(B54)</f>
         <v/>
@@ -3551,7 +4227,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M55" s="9" t="str" cm="1">
         <f t="array" ref="M55">PAGE_NAME(B55)</f>
         <v/>
@@ -3561,7 +4237,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M56" s="9" t="str" cm="1">
         <f t="array" ref="M56">PAGE_NAME(B56)</f>
         <v/>
@@ -3571,7 +4247,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M57" s="9" t="str" cm="1">
         <f t="array" ref="M57">PAGE_NAME(B57)</f>
         <v/>
@@ -3581,7 +4257,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M58" s="9" t="str" cm="1">
         <f t="array" ref="M58">PAGE_NAME(B58)</f>
         <v/>
@@ -3591,7 +4267,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M59" s="9" t="str" cm="1">
         <f t="array" ref="M59">PAGE_NAME(B59)</f>
         <v/>
@@ -3601,7 +4277,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M60" s="9" t="str" cm="1">
         <f t="array" ref="M60">PAGE_NAME(B60)</f>
         <v/>
@@ -3611,7 +4287,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M61" s="9" t="str" cm="1">
         <f t="array" ref="M61">PAGE_NAME(B61)</f>
         <v/>
@@ -3621,7 +4297,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M62" s="9" t="str" cm="1">
         <f t="array" ref="M62">PAGE_NAME(B62)</f>
         <v/>
@@ -3631,7 +4307,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M63" s="9" t="str" cm="1">
         <f t="array" ref="M63">PAGE_NAME(B63)</f>
         <v/>
@@ -3641,7 +4317,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="13:14" ht="16" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="M64" s="9" t="str" cm="1">
         <f t="array" ref="M64">PAGE_NAME(B64)</f>
         <v/>
@@ -6535,6 +7211,18 @@
     <hyperlink ref="B18" r:id="rId11" xr:uid="{20179303-1494-4F18-AD01-277E0C7BB1D9}"/>
     <hyperlink ref="B19" r:id="rId12" xr:uid="{8D393304-929D-44EF-B222-2BA41A60FAF3}"/>
     <hyperlink ref="B33" r:id="rId13" xr:uid="{7CFDA509-E5F9-4C63-B13E-6843A66E58AA}"/>
+    <hyperlink ref="B50" r:id="rId14" xr:uid="{EE4E13C0-27BA-4647-8F3C-6FB32E6D7D7B}"/>
+    <hyperlink ref="B49" r:id="rId15" xr:uid="{05495B7C-D737-42AD-96FB-0C7CD557B8ED}"/>
+    <hyperlink ref="B47" r:id="rId16" xr:uid="{6F11DF63-136D-47A1-8F96-4149C15C6D6B}"/>
+    <hyperlink ref="B46" r:id="rId17" xr:uid="{194D5225-B161-4647-9183-9AE5A9DEE0CA}"/>
+    <hyperlink ref="B42" r:id="rId18" xr:uid="{4C6F68B6-982E-4E0B-94C9-5F062544121D}"/>
+    <hyperlink ref="B41" r:id="rId19" xr:uid="{56F9D1F2-D7EA-407F-8DC5-4038731BB6CA}"/>
+    <hyperlink ref="B40" r:id="rId20" xr:uid="{42E3FE8A-B27F-4558-A369-1CBCC30608FA}"/>
+    <hyperlink ref="B39" r:id="rId21" xr:uid="{C79A7B16-04DF-4BDB-B70A-902E2FAC8DDC}"/>
+    <hyperlink ref="B38" r:id="rId22" xr:uid="{B41AF856-ED80-4678-877B-279C78ECBCC1}"/>
+    <hyperlink ref="B37" r:id="rId23" xr:uid="{F1B93BA5-2027-4C4E-8F57-E4377BE9F923}"/>
+    <hyperlink ref="B35" r:id="rId24" xr:uid="{00DA40D3-ABC8-4AA3-B05F-507AD207B01B}"/>
+    <hyperlink ref="B34" r:id="rId25" xr:uid="{8490BADF-6BB2-4CF2-8F32-70ACBE433D5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -6556,7 +7244,7 @@
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K1048576 U2:U37 I2:I1048576</xm:sqref>
+          <xm:sqref>K2:K1048576 U2:U50 I2:I1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6565,6 +7253,422 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FC6DF9-AFDB-4043-86D4-EAF69A625189}">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="37.08203125" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27.4140625" customWidth="1"/>
+    <col min="4" max="4" width="51.4140625" customWidth="1"/>
+    <col min="5" max="5" width="103.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="47"/>
+      <c r="D2" s="49" cm="1">
+        <f t="array" ref="D2">ROWS(_xlfn.UNIQUE(TRANSPOSE(_xlfn.TEXTSPLIT(_xlfn.TEXTJOIN(";",TRUE,
+          _xlfn._xlws.FILTER(Requirements!V:V,Requirements!U:U="yes")),
+      ";")))) / 42 * 100</f>
+        <v>61.904761904761905</v>
+      </c>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="47"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="47"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="47"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="47"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="47"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="47"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="47"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="47"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="47"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="47"/>
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="47"/>
+    </row>
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="47"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="47"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="47"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="47"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="47"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="47"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="47"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="47"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="47"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="47"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="47"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="47"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="47"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="47"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="47"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="47"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="47"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="47"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="47"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="47"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>176</v>
+      </c>
+      <c r="B37" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="47"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="47"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="47"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="47"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="47"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="47"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="47"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C323F474-BE25-4449-9222-E1A46A1843B5}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
@@ -6574,21 +7678,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="409" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="43"/>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" ht="82" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -6649,7 +7753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49B4E29-A057-6044-8543-9F9FC3A9F2DF}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
@@ -6694,7 +7798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB89888-9517-1640-A922-49BDADD5811C}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
@@ -6770,33 +7874,56 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
-    <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <xsd:import namespace="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <xsd:import namespace="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document - Suivi de projet" ma:contentTypeID="0x010100333226B5D6902549BFE4A72F45A4400B0100C4EDCC502392C74593E3C9394BE47D50" ma:contentTypeVersion="77" ma:contentTypeDescription="Type de contenu - Documentation de suivi de projet" ma:contentTypeScope="" ma:versionID="750307453bd57e11359b73b96e3aab16">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xmlns:ns3="4d1bcb53-8342-451f-9a55-9ed7ce9077fe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6a2f13b6130fedcc70d6c0bdc11f1fe" ns1:_="" ns2:_="" ns3:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="f6ca01e7-bd19-41f1-999c-e032ef5104c3"/>
+    <xsd:import namespace="4d1bcb53-8342-451f-9a55-9ed7ce9077fe"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:Description" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:SortOrder" minOccurs="0"/>
+                <xsd:element ref="ns2:Référence_x0020_Documentaire" minOccurs="0"/>
+                <xsd:element ref="ns2:Ticket_x0020_Changement" minOccurs="0"/>
+                <xsd:element ref="ns2:Environnement" minOccurs="0"/>
+                <xsd:element ref="ns2:Chantier" minOccurs="0"/>
+                <xsd:element ref="ns2:Référence_x0020_Bon_x0020_de_x0020_Commande" minOccurs="0"/>
+                <xsd:element ref="ns2:Durée_x0020_d_x0027_Utilité_x0020_Administrative_x0020__x0028_DUA_x0029_" minOccurs="0"/>
+                <xsd:element ref="ns1:_ExtendedDescription" minOccurs="0"/>
+                <xsd:element ref="ns2:CreateurAlfresco" minOccurs="0"/>
+                <xsd:element ref="ns2:ModificateurAlfresco" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:l0a6b4600f484920bbceae0813174244" minOccurs="0"/>
+                <xsd:element ref="ns2:b2804ef99be44b9e8166e80a6c2eb9f1" minOccurs="0"/>
+                <xsd:element ref="ns2:eef0f6fc4ed046399a9d01fd3a7d6a6a" minOccurs="0"/>
+                <xsd:element ref="ns2:p671c8df16a44846939d278d4958f62c" minOccurs="0"/>
+                <xsd:element ref="ns2:b084a4cb34a444d7969136255594d2f3" minOccurs="0"/>
+                <xsd:element ref="ns2:m9a76db3058146ae844db6599c9d7036" minOccurs="0"/>
+                <xsd:element ref="ns2:mc4aa6e782e045f6bb87dab01c971b56" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAllLabel" minOccurs="0"/>
+                <xsd:element ref="ns2:g30fb2d8061a4d40b63138f91c1a832e" minOccurs="0"/>
+                <xsd:element ref="ns2:m312bc62cb0243b6a873cbbf4dace6b2" minOccurs="0"/>
+                <xsd:element ref="ns2:f8b6baa267c0456bbf6a8d18c49a130b" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6804,104 +7931,10 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="eebd8b74-b9de-41b2-9247-c010c4973c2b" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Description" ma:index="14" nillable="true" ma:displayName="Description" ma:format="Dropdown" ma:internalName="Description">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="18" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4ea1a638-fe8f-4e55-a8a3-ec1a1fdf419b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="SortOrder" ma:index="24" nillable="true" ma:displayName="Sort Order" ma:format="Dropdown" ma:internalName="SortOrder" ma:percentage="FALSE">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Number"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b7009bbd-f938-489b-a530-f05273710fff" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="_ExtendedDescription" ma:index="18" nillable="true" ma:displayName="Description" ma:internalName="_ExtendedDescription">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6909,10 +7942,64 @@
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5a44311-ed64-4a72-909f-c9dc6973bde2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f6ca01e7-bd19-41f1-999c-e032ef5104c3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{eb2147c2-73e8-4ace-b987-f4badfc2b106}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b7009bbd-f938-489b-a530-f05273710fff">
+    <xsd:element name="Référence_x0020_Documentaire" ma:index="7" nillable="true" ma:displayName="Référence Documentaire" ma:default="" ma:internalName="R_x00e9_f_x00e9_rence_x0020_Documentaire">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Ticket_x0020_Changement" ma:index="8" nillable="true" ma:displayName="Ticket Changement" ma:default="" ma:internalName="Ticket_x0020_Changement">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Environnement" ma:index="9" nillable="true" ma:displayName="Environnement" ma:default="" ma:internalName="Environnement">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Chantier" ma:index="11" nillable="true" ma:displayName="Chantier" ma:default="" ma:internalName="Chantier">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Référence_x0020_Bon_x0020_de_x0020_Commande" ma:index="13" nillable="true" ma:displayName="Référence Bon de Commande" ma:indexed="true" ma:internalName="R_x00e9_f_x00e9_rence_x0020_Bon_x0020_de_x0020_Commande">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Durée_x0020_d_x0027_Utilité_x0020_Administrative_x0020__x0028_DUA_x0029_" ma:index="17" nillable="true" ma:displayName="Durée d'Utilité Administrative (DUA)" ma:internalName="Dur_x00e9_e_x0020_d_x0027_Utilit_x00e9__x0020_Administrative_x0020__x0028_DUA_x0029_" ma:percentage="FALSE">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Number"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="CreateurAlfresco" ma:index="19" nillable="true" ma:displayName="CreateurAlfresco" ma:default="" ma:internalName="CreateurAlfresco">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ModificateurAlfresco" ma:index="20" nillable="true" ma:displayName="ModificateurAlfresco" ma:default="" ma:internalName="ModificateurAlfresco">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{61f3ec5f-5a67-40e0-b5e0-e23b6b588f8b}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -6922,6 +8009,140 @@
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="l0a6b4600f484920bbceae0813174244" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="l0a6b4600f484920bbceae0813174244" ma:taxonomyFieldName="Prestataire_x0028_s_x0029_" ma:displayName="Prestataire(s)" ma:fieldId="{50a6b460-0f48-4920-bbce-ae0813174244}" ma:taxonomyMulti="true" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="46ab08c7-aeb3-4684-9e81-fb4503d52906" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="b2804ef99be44b9e8166e80a6c2eb9f1" ma:index="24" nillable="true" ma:taxonomy="true" ma:internalName="b2804ef99be44b9e8166e80a6c2eb9f1" ma:taxonomyFieldName="Statut_x0020_du_x0020_document" ma:displayName="Statut du document" ma:default="" ma:fieldId="{b2804ef9-9be4-4b9e-8166-e80a6c2eb9f1}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="57d84b5c-8637-4a53-9541-e98f138eeb73" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="eef0f6fc4ed046399a9d01fd3a7d6a6a" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="eef0f6fc4ed046399a9d01fd3a7d6a6a" ma:taxonomyFieldName="Sort_x0020_Final_x0020__x0028_Archivage_x0029_1" ma:displayName="Sort Final (Archivage)" ma:indexed="true" ma:fieldId="{eef0f6fc-4ed0-4639-9a9d-01fd3a7d6a6a}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="894a0867-9216-43ab-99c5-e7b2cbb034e6" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="p671c8df16a44846939d278d4958f62c" ma:index="28" nillable="true" ma:taxonomy="true" ma:internalName="p671c8df16a44846939d278d4958f62c" ma:taxonomyFieldName="Direction_x0020__x002F__x0020_Service" ma:displayName="Direction / Service" ma:readOnly="false" ma:fieldId="{9671c8df-16a4-4846-939d-278d4958f62c}" ma:taxonomyMulti="true" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="06452e41-1966-4633-9fe1-38f9847c7dc7" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="b084a4cb34a444d7969136255594d2f3" ma:index="30" nillable="true" ma:taxonomy="true" ma:internalName="b084a4cb34a444d7969136255594d2f3" ma:taxonomyFieldName="Type_x0020_de_x0020_document_x0020_ANS" ma:displayName="Type de document ANS" ma:indexed="true" ma:readOnly="false" ma:default="" ma:fieldId="{b084a4cb-34a4-44d7-9691-36255594d2f3}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="1275da89-553e-403a-abbb-5d47ef289756" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="m9a76db3058146ae844db6599c9d7036" ma:index="32" nillable="true" ma:taxonomy="true" ma:internalName="m9a76db3058146ae844db6599c9d7036" ma:taxonomyFieldName="Classification" ma:displayName="Classification" ma:readOnly="false" ma:fieldId="{69a76db3-0581-46ae-844d-b6599c9d7036}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="8feb0b63-8672-4f69-8e69-5df4ee99fafe" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="mc4aa6e782e045f6bb87dab01c971b56" ma:index="33" nillable="true" ma:taxonomy="true" ma:internalName="mc4aa6e782e045f6bb87dab01c971b56" ma:taxonomyFieldName="Version_x0020_Applicative" ma:displayName="Version Applicative" ma:default="" ma:fieldId="{6c4aa6e7-82e0-45f6-bb87-dab01c971b56}" ma:taxonomyMulti="true" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="3d1661bf-2cce-4a88-b69a-0a25d82a555a" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAllLabel" ma:index="34" nillable="true" ma:displayName="Taxonomy Catch All Column1" ma:hidden="true" ma:list="{61f3ec5f-5a67-40e0-b5e0-e23b6b588f8b}" ma:internalName="TaxCatchAllLabel" ma:readOnly="true" ma:showField="CatchAllDataLabel" ma:web="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="g30fb2d8061a4d40b63138f91c1a832e" ma:index="35" nillable="true" ma:taxonomy="true" ma:internalName="g30fb2d8061a4d40b63138f91c1a832e" ma:taxonomyFieldName="March_x00e9_" ma:displayName="Marché" ma:fieldId="{030fb2d8-061a-4d40-b631-38f91c1a832e}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="e41f313d-41ce-4da8-b34e-2b8403642257" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="m312bc62cb0243b6a873cbbf4dace6b2" ma:index="37" nillable="true" ma:taxonomy="true" ma:internalName="m312bc62cb0243b6a873cbbf4dace6b2" ma:taxonomyFieldName="Projet" ma:displayName="Projet" ma:readOnly="false" ma:fieldId="{6312bc62-cb02-43b6-a873-cbbf4dace6b2}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="207e172a-6847-42a8-b45e-d0bbb1e23407" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="f8b6baa267c0456bbf6a8d18c49a130b" ma:index="38" nillable="true" ma:taxonomy="true" ma:internalName="f8b6baa267c0456bbf6a8d18c49a130b" ma:taxonomyFieldName="Cat_x00e9_gorie_x0020_Documentaire" ma:displayName="Catégorie Documentaire" ma:readOnly="false" ma:fieldId="{f8b6baa2-67c0-456b-bf6a-8d18c49a130b}" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="5548a444-67a9-4fed-ab61-d9aae03cf8ed" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4d1bcb53-8342-451f-9a55-9ed7ce9077fe" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="39" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="40" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="41" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="43" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4480557-28ee-4200-b705-f4b4ceb9c11a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="44" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="45" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="46" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="47" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="48" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -6933,8 +8154,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="36" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="1" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7023,38 +8244,74 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+    <TaxCatchAll xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4d1bcb53-8342-451f-9a55-9ed7ce9077fe">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <ModificateurAlfresco xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <Référence_x0020_Documentaire xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <Référence_x0020_Bon_x0020_de_x0020_Commande xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <eef0f6fc4ed046399a9d01fd3a7d6a6a xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </eef0f6fc4ed046399a9d01fd3a7d6a6a>
+    <f8b6baa267c0456bbf6a8d18c49a130b xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f8b6baa267c0456bbf6a8d18c49a130b>
+    <Chantier xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <Environnement xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <Durée_x0020_d_x0027_Utilité_x0020_Administrative_x0020__x0028_DUA_x0029_ xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <p671c8df16a44846939d278d4958f62c xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </p671c8df16a44846939d278d4958f62c>
+    <_ExtendedDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <b2804ef99be44b9e8166e80a6c2eb9f1 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </b2804ef99be44b9e8166e80a6c2eb9f1>
+    <mc4aa6e782e045f6bb87dab01c971b56 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </mc4aa6e782e045f6bb87dab01c971b56>
+    <m312bc62cb0243b6a873cbbf4dace6b2 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </m312bc62cb0243b6a873cbbf4dace6b2>
+    <b084a4cb34a444d7969136255594d2f3 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </b084a4cb34a444d7969136255594d2f3>
+    <CreateurAlfresco xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <g30fb2d8061a4d40b63138f91c1a832e xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </g30fb2d8061a4d40b63138f91c1a832e>
+    <Ticket_x0020_Changement xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3" xsi:nil="true"/>
+    <m9a76db3058146ae844db6599c9d7036 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </m9a76db3058146ae844db6599c9d7036>
+    <l0a6b4600f484920bbceae0813174244 xmlns="f6ca01e7-bd19-41f1-999c-e032ef5104c3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </l0a6b4600f484920bbceae0813174244>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E19681A-8DD3-40CB-9262-8533E89B98A6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C310A00-BCF3-463C-98B1-891E51C6FD1A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="f6ca01e7-bd19-41f1-999c-e032ef5104c3"/>
+    <ds:schemaRef ds:uri="4d1bcb53-8342-451f-9a55-9ed7ce9077fe"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -7065,21 +8322,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="4d1bcb53-8342-451f-9a55-9ed7ce9077fe"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f6ca01e7-bd19-41f1-999c-e032ef5104c3"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>